--- a/结果/结果提交.xlsx
+++ b/结果/结果提交.xlsx
@@ -1216,14 +1216,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S011→O01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1252.5</v>
+        <v>1220.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2861</v>
+        <v>1.1937</v>
       </c>
     </row>
     <row r="3">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O01→S005→S004→O01</t>
+          <t>O01→S013→O01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2421</v>
+        <v>1612.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2199</v>
+        <v>2.0253</v>
       </c>
     </row>
     <row r="4">
@@ -1288,14 +1288,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O01→S001→S013→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1964.5</v>
+        <v>1312.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1575</v>
+        <v>1.3096</v>
       </c>
     </row>
     <row r="5">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S009→S002→S013→O01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1252.5</v>
+        <v>2678.9</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2861</v>
+        <v>3.3978</v>
       </c>
     </row>
     <row r="6">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>O01→S014→O01</t>
+          <t>O01→S012→O01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1868.6</v>
+        <v>1923.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1373</v>
+        <v>2.7555</v>
       </c>
     </row>
     <row r="7">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>O01→S010→O01</t>
+          <t>O01→S014→O01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1554.6</v>
+        <v>1868.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8211</v>
+        <v>2.1373</v>
       </c>
     </row>
     <row r="8">
@@ -1432,14 +1432,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2111</v>
+        <v>1627.4</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8718</v>
+        <v>3.0047</v>
       </c>
     </row>
     <row r="9">
@@ -1468,14 +1468,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O01→S001→S006→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2257.3</v>
+        <v>1561.4</v>
       </c>
       <c r="H9" t="n">
-        <v>5.12</v>
+        <v>2.9263</v>
       </c>
     </row>
     <row r="10">
@@ -1500,18 +1500,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1252.5</v>
+        <v>1220.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3260.3</v>
+        <v>2533.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0283</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="11">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1536,18 +1536,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1252.5</v>
+        <v>1312.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O01→S013→O01</t>
+          <t>O01→S005→O01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2864.6</v>
+        <v>3008.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0253</v>
+        <v>2.2015</v>
       </c>
     </row>
     <row r="12">
@@ -1558,32 +1558,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1554.6</v>
+        <v>1561.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O01→S012→O01</t>
+          <t>O01→S006→S007→O01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3478.5</v>
+        <v>3975.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7555</v>
+        <v>4.2979</v>
       </c>
     </row>
     <row r="13">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1868.6</v>
+        <v>1627.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S002→O01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3774.5</v>
+        <v>3804.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7735</v>
+        <v>6.301</v>
       </c>
     </row>
     <row r="14">
@@ -1630,32 +1630,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2111</v>
+        <v>1868.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S010→O01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4672.4</v>
+        <v>3423.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5676</v>
+        <v>1.8211</v>
       </c>
     </row>
     <row r="15">
@@ -1666,32 +1666,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A-B01</t>
+          <t>B-B04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2124</v>
+        <v>1923.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S004→O01</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3436.6</v>
+        <v>3849.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.355</v>
+        <v>3.047</v>
       </c>
     </row>
     <row r="16">
@@ -1702,32 +1702,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>A-B01</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2257.3</v>
+        <v>2065.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>O01→S001→S005→O01</t>
+          <t>O01→S009→O01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4632.8</v>
+        <v>3757</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5861</v>
+        <v>2.3383</v>
       </c>
     </row>
     <row r="17">
@@ -1738,32 +1738,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3478.5</v>
+        <v>2533.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S015→S003→O01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5444.4</v>
+        <v>5077.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9861</v>
+        <v>3.3367</v>
       </c>
     </row>
     <row r="18">
@@ -1774,32 +1774,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B-B01</t>
+          <t>A-B02</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3774.5</v>
+        <v>2697.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>O01→S015→O01</t>
+          <t>O01→S011→S015→O01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5604.1</v>
+        <v>4970.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.311</v>
+        <v>2.5833</v>
       </c>
     </row>
     <row r="19">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C-B02</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4632.8</v>
+        <v>3461.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7392.2</v>
+        <v>5427.3</v>
       </c>
       <c r="H19" t="n">
-        <v>6.082</v>
+        <v>2.9861</v>
       </c>
     </row>
     <row r="20">
@@ -1856,22 +1856,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C-B01</t>
+          <t>C-B02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4672.4</v>
+        <v>3804.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>O01→S011→S004→O01</t>
+          <t>O01→S005→S004→O01</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7362.3</v>
+        <v>6522.3</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2895</v>
+        <v>6.3448</v>
       </c>
     </row>
     <row r="21">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1892,22 +1892,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>B-B01</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5444.4</v>
+        <v>3849.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>O01→S005→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>6963.4</v>
+        <v>5755.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0942</v>
+        <v>2.7735</v>
       </c>
     </row>
     <row r="22">
@@ -1918,32 +1918,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>C-B01</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5643</v>
+        <v>3975.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>O01→S009→O01</t>
+          <t>O01→S003→O01</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7203.8</v>
+        <v>6477.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1025</v>
+        <v>6.3228</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q2-T01</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>909.4</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="3">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="4">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2-T04</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3530.2</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="6">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3530.2</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="7">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>939.4</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="8">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="9">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1104.9</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="10">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1104.9</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="11">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q2-T04</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="12">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="13">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1104.9</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="14">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>939.4</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="15">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3530.2</v>
+        <v>1314.9</v>
       </c>
     </row>
     <row r="16">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q2-T01</t>
+          <t>Q2-T08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>909.4</v>
+        <v>1248.9</v>
       </c>
     </row>
     <row r="17">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="18">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2-T09</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2538.3</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="19">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="20">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="21">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="22">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q2-T09</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2538.3</v>
+        <v>1527.9</v>
       </c>
     </row>
     <row r="23">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="24">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q2-T07</t>
+          <t>Q2-T12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
     </row>
     <row r="25">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="26">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="27">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="28">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="29">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3882</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="30">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6601.7</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="31">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6601.7</v>
+        <v>4223.9</v>
       </c>
     </row>
     <row r="32">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3882</v>
+        <v>5686.6</v>
       </c>
     </row>
     <row r="33">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
     </row>
     <row r="34">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
     </row>
     <row r="35">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6642.7</v>
+        <v>5802.7</v>
       </c>
     </row>
     <row r="36">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1610.6</v>
+        <v>5802.7</v>
       </c>
     </row>
     <row r="37">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6642.7</v>
+        <v>3168.4</v>
       </c>
     </row>
     <row r="38">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6642.7</v>
+        <v>3168.4</v>
       </c>
     </row>
     <row r="39">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q2-T02</t>
+          <t>Q2-T10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1100.6</v>
+        <v>2443.2</v>
       </c>
     </row>
     <row r="40">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4127.4</v>
+        <v>5167.1</v>
       </c>
     </row>
     <row r="41">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4127.4</v>
+        <v>5167.1</v>
       </c>
     </row>
     <row r="42">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2-T20</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6486.7</v>
+        <v>5167.1</v>
       </c>
     </row>
     <row r="43">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q2-T20</t>
+          <t>Q2-T19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6486.7</v>
+        <v>5167.1</v>
       </c>
     </row>
     <row r="44">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q2-T15</t>
+          <t>Q2-T10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4127.4</v>
+        <v>2443.2</v>
       </c>
     </row>
     <row r="45">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q2-T14</t>
+          <t>Q2-T09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3059.1</v>
+        <v>2155.7</v>
       </c>
     </row>
     <row r="46">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1905.6</v>
+        <v>2656.5</v>
       </c>
     </row>
     <row r="47">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1905.6</v>
+        <v>935.1</v>
       </c>
     </row>
     <row r="48">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1905.6</v>
+        <v>2155.7</v>
       </c>
     </row>
     <row r="49">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q2-T14</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3059.1</v>
+        <v>2656.5</v>
       </c>
     </row>
     <row r="50">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2-T08</t>
+          <t>Q2-T03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1905.6</v>
+        <v>935.1</v>
       </c>
     </row>
     <row r="51">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5962.5</v>
+        <v>3415.4</v>
       </c>
     </row>
     <row r="52">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q2-T18</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5962.5</v>
+        <v>3415.4</v>
       </c>
     </row>
     <row r="53">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
     </row>
     <row r="54">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
     </row>
     <row r="55">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q2-T13</t>
+          <t>Q2-T11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3386.8</v>
+        <v>3415.4</v>
       </c>
     </row>
     <row r="56">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
     </row>
     <row r="57">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q2-T12</t>
+          <t>Q2-T20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3101.8</v>
+        <v>5082.8</v>
       </c>
     </row>
     <row r="58">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
     </row>
     <row r="59">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q2-T16</t>
+          <t>Q2-T18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4771.7</v>
+        <v>4754.6</v>
       </c>
     </row>
     <row r="60">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q2-T12</t>
+          <t>Q2-T20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3101.8</v>
+        <v>5082.8</v>
       </c>
     </row>
     <row r="61">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6735</v>
+        <v>3192.8</v>
       </c>
     </row>
     <row r="62">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6735</v>
+        <v>1127.4</v>
       </c>
     </row>
     <row r="63">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2-T21</t>
+          <t>Q2-T15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6735</v>
+        <v>3192.8</v>
       </c>
     </row>
     <row r="64">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
     </row>
     <row r="65">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
     </row>
     <row r="66">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2-T06</t>
+          <t>Q2-T13</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1084.8</v>
+        <v>2953.4</v>
       </c>
     </row>
     <row r="67">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5795.1</v>
+        <v>892.5</v>
       </c>
     </row>
     <row r="68">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5795.1</v>
+        <v>3589.7</v>
       </c>
     </row>
     <row r="69">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2-T19</t>
+          <t>Q2-T01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5795.1</v>
+        <v>892.5</v>
       </c>
     </row>
     <row r="70">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="71">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="72">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q2-T11</t>
+          <t>Q2-T05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="73">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2-T10</t>
+          <t>Q2-T02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2336</v>
+        <v>1083.6</v>
       </c>
     </row>
     <row r="74">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q2-T03</t>
+          <t>Q2-T04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1436</v>
+        <v>2150.4</v>
       </c>
     </row>
     <row r="75">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q2-T10</t>
+          <t>Q2-T02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2336</v>
+        <v>1083.6</v>
       </c>
     </row>
     <row r="76">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q2-T05</t>
+          <t>Q2-T06</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q2-T17</t>
+          <t>Q2-T16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4992.7</v>
+        <v>3761.8</v>
       </c>
     </row>
     <row r="80">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4992.7</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="81">
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4992.7</v>
+        <v>4259</v>
       </c>
     </row>
   </sheetData>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64.3</v>
+        <v>59.04</v>
       </c>
       <c r="E2" t="n">
-        <v>109.279108</v>
+        <v>109.278483</v>
       </c>
       <c r="F2" t="n">
-        <v>23.01896</v>
+        <v>23.02146</v>
       </c>
       <c r="G2" t="n">
-        <v>696.8</v>
+        <v>663.2</v>
       </c>
       <c r="H2" t="n">
-        <v>754.8</v>
+        <v>741.79</v>
       </c>
       <c r="I2" t="n">
-        <v>3104.3</v>
+        <v>3452.09</v>
       </c>
       <c r="J2" t="n">
-        <v>3632.2</v>
+        <v>3969.47</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9938</v>
+        <v>1.1014</v>
       </c>
     </row>
     <row r="3">
@@ -3711,28 +3711,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2419.7</v>
+        <v>2128.58</v>
       </c>
       <c r="E3" t="n">
-        <v>109.201358</v>
+        <v>109.201483</v>
       </c>
       <c r="F3" t="n">
-        <v>23.03296</v>
+        <v>23.032835</v>
       </c>
       <c r="G3" t="n">
-        <v>675.4</v>
+        <v>672.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3037.5</v>
+        <v>2744.37</v>
       </c>
       <c r="I3" t="n">
-        <v>6676.9</v>
+        <v>5999.19</v>
       </c>
       <c r="J3" t="n">
-        <v>7130.3</v>
+        <v>6450.38</v>
       </c>
       <c r="K3" t="n">
-        <v>1.343</v>
+        <v>1.2244</v>
       </c>
     </row>
     <row r="4">
@@ -3748,32 +3748,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>M03</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5261.8</v>
+        <v>4759.15</v>
       </c>
       <c r="E4" t="n">
-        <v>109.228858</v>
+        <v>109.247608</v>
       </c>
       <c r="F4" t="n">
-        <v>23.06271</v>
+        <v>23.056585</v>
       </c>
       <c r="G4" t="n">
-        <v>528.3</v>
+        <v>586.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5974</v>
+        <v>5458.13</v>
       </c>
       <c r="I4" t="n">
-        <v>6601.2</v>
+        <v>6032.73</v>
       </c>
       <c r="J4" t="n">
-        <v>7136.8</v>
+        <v>6559.95</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4933</v>
+        <v>0.4647</v>
       </c>
     </row>
   </sheetData>
@@ -3787,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3830,14 +3830,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O01→S002 爬升</t>
+          <t>O01→S013 爬升</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>450.4</v>
+        <v>450.49</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3854,14 +3854,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S013 巡航</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>450.4</v>
+        <v>450.49</v>
       </c>
       <c r="D3" t="n">
-        <v>780.4</v>
+        <v>778.0599999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S013 巡航</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>780.4</v>
+        <v>778.0599999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1070</v>
+        <v>854.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3906,14 +3906,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O01→S002 下降</t>
+          <t>O01→S013 下降</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1070</v>
+        <v>854.58</v>
       </c>
       <c r="D5" t="n">
-        <v>1105.8</v>
+        <v>873.5700000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3934,14 +3934,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S002 投送</t>
+          <t>S013 投送</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1105.8</v>
+        <v>873.5700000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1315.8</v>
+        <v>1083.57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3962,14 +3962,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S002→S013 爬升</t>
+          <t>S013→O01 爬升</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1315.8</v>
+        <v>1083.57</v>
       </c>
       <c r="D7" t="n">
-        <v>1368.4</v>
+        <v>1099.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3990,14 +3990,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S002→S013 巡航</t>
+          <t>S013→O01 巡航</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1368.4</v>
+        <v>1099.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1748.1</v>
+        <v>1503.48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4018,14 +4018,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S002→S013 下降</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1748.1</v>
+        <v>1503.48</v>
       </c>
       <c r="D9" t="n">
-        <v>1758.3</v>
+        <v>1587.29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4046,129 +4046,125 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S013 投送</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1758.3</v>
+        <v>1587.29</v>
       </c>
       <c r="D10" t="n">
-        <v>1938.3</v>
+        <v>1612.07</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S013→O01 爬升</t>
+          <t>O01→S009 爬升</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1938.3</v>
+        <v>390</v>
       </c>
       <c r="D11" t="n">
-        <v>1954.1</v>
+        <v>445.18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1954.1</v>
+        <v>445.18</v>
       </c>
       <c r="D12" t="n">
-        <v>2030.1</v>
+        <v>773.17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2030.1</v>
+        <v>773.17</v>
       </c>
       <c r="D13" t="n">
-        <v>2358.2</v>
+        <v>922.08</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S013→O01 下降</t>
+          <t>O01→S009 下降</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2358.2</v>
+        <v>922.08</v>
       </c>
       <c r="D14" t="n">
-        <v>2466.8</v>
+        <v>947.37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4178,21 +4174,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S009 投送</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>390</v>
+        <v>947.37</v>
       </c>
       <c r="D15" t="n">
-        <v>438.5</v>
+        <v>1127.37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4202,21 +4202,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S009→S002 爬升</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>438.5</v>
+        <v>1127.37</v>
       </c>
       <c r="D16" t="n">
-        <v>693.7</v>
+        <v>1160.13</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4226,21 +4230,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S009→S002 巡航</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>693.7</v>
+        <v>1160.13</v>
       </c>
       <c r="D17" t="n">
-        <v>729.4</v>
+        <v>1304.38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4250,21 +4258,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S009→S002 下降</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>729.4</v>
+        <v>1304.38</v>
       </c>
       <c r="D18" t="n">
-        <v>969.4</v>
+        <v>1347.89</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4274,21 +4286,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S002 投送</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>969.4</v>
+        <v>1347.89</v>
       </c>
       <c r="D19" t="n">
-        <v>999</v>
+        <v>1527.89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4298,21 +4314,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S002→S013 爬升</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>999</v>
+        <v>1527.89</v>
       </c>
       <c r="D20" t="n">
-        <v>1254.3</v>
+        <v>1580.46</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4322,86 +4342,98 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S002→S013 巡航</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1254.3</v>
+        <v>1580.46</v>
       </c>
       <c r="D21" t="n">
-        <v>1312.5</v>
+        <v>1960.17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>O01→S013 爬升</t>
+          <t>S002→S013 下降</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>360</v>
+        <v>1960.17</v>
       </c>
       <c r="D22" t="n">
-        <v>450.5</v>
+        <v>1970.38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O01→S013 巡航</t>
+          <t>S013 投送</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>450.5</v>
+        <v>1970.38</v>
       </c>
       <c r="D23" t="n">
-        <v>780.5</v>
+        <v>2150.38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>O01→S013 巡航</t>
+          <t>S013→O01 爬升</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>780.5</v>
+        <v>2150.38</v>
       </c>
       <c r="D24" t="n">
-        <v>854.6</v>
+        <v>2166.21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4417,19 +4449,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>O01→S013 下降</t>
+          <t>S013→O01 巡航</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>854.6</v>
+        <v>2166.21</v>
       </c>
       <c r="D25" t="n">
-        <v>873.6</v>
+        <v>2570.29</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4445,19 +4477,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S013 投送</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>873.6</v>
+        <v>2570.29</v>
       </c>
       <c r="D26" t="n">
-        <v>1083.6</v>
+        <v>2654.09</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4473,30 +4505,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S013→O01 爬升</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1083.6</v>
+        <v>2654.09</v>
       </c>
       <c r="D27" t="n">
-        <v>1099.4</v>
+        <v>2678.88</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4506,25 +4534,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1099.4</v>
+        <v>360</v>
       </c>
       <c r="D28" t="n">
-        <v>1175.4</v>
+        <v>439.47</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4534,14 +4558,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1175.4</v>
+        <v>439.47</v>
       </c>
       <c r="D29" t="n">
-        <v>1503.5</v>
+        <v>704.55</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4558,14 +4582,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S013→O01 下降</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1503.5</v>
+        <v>704.55</v>
       </c>
       <c r="D30" t="n">
-        <v>1612.1</v>
+        <v>725.0700000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4577,19 +4601,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>O01→S006 爬升</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>360</v>
+        <v>725.0700000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>439.5</v>
+        <v>935.0700000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4601,19 +4625,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O01→S006 巡航</t>
+          <t>S006→O01 爬升</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>439.5</v>
+        <v>935.0700000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>704.6</v>
+        <v>952.17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4625,19 +4649,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O01→S006 下降</t>
+          <t>S006→O01 巡航</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>704.6</v>
+        <v>952.17</v>
       </c>
       <c r="D33" t="n">
-        <v>725.1</v>
+        <v>1217.25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4649,19 +4673,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S006 投送</t>
+          <t>S006→O01 下降</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>725.1</v>
+        <v>1217.25</v>
       </c>
       <c r="D34" t="n">
-        <v>935.1</v>
+        <v>1312.61</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -4678,14 +4702,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S006→O01 爬升</t>
+          <t>O01→S009 爬升</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>935.1</v>
+        <v>360</v>
       </c>
       <c r="D35" t="n">
-        <v>952.2</v>
+        <v>415.18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4702,14 +4726,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S006→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>952.2</v>
+        <v>415.18</v>
       </c>
       <c r="D36" t="n">
-        <v>1217.3</v>
+        <v>743.22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -4726,86 +4750,98 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S006→O01 下降</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1217.3</v>
+        <v>743.22</v>
       </c>
       <c r="D37" t="n">
-        <v>1312.6</v>
+        <v>892.08</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>O01→S014 爬升</t>
+          <t>O01→S009 下降</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>390</v>
+        <v>892.08</v>
       </c>
       <c r="D38" t="n">
-        <v>544.7</v>
+        <v>917.37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>O01→S014 巡航</t>
+          <t>S009 投送</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>544.7</v>
+        <v>917.37</v>
       </c>
       <c r="D39" t="n">
-        <v>807.7</v>
+        <v>1127.37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>O01→S014 巡航</t>
+          <t>S009→O01 爬升</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>807.7</v>
+        <v>1127.37</v>
       </c>
       <c r="D40" t="n">
-        <v>905.5</v>
+        <v>1148.45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -4821,19 +4857,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>O01→S014 下降</t>
+          <t>S009→O01 巡航</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>905.5</v>
+        <v>1148.45</v>
       </c>
       <c r="D41" t="n">
-        <v>1001.9</v>
+        <v>1625.35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4849,19 +4885,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S014 投送</t>
+          <t>S009→O01 下降</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1001.9</v>
+        <v>1625.35</v>
       </c>
       <c r="D42" t="n">
-        <v>1241.9</v>
+        <v>1666.78</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4877,30 +4913,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S014→O01 爬升</t>
+          <t>S009→O01 下降</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1241.9</v>
+        <v>1666.78</v>
       </c>
       <c r="D43" t="n">
-        <v>1322.2</v>
+        <v>1691.56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4910,25 +4942,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S014→O01 巡航</t>
+          <t>O01→S012 爬升</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1322.2</v>
+        <v>390</v>
       </c>
       <c r="D44" t="n">
-        <v>1421.2</v>
+        <v>485.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4938,14 +4966,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S014→O01 巡航</t>
+          <t>O01→S012 巡航</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1421.2</v>
+        <v>485.2</v>
       </c>
       <c r="D45" t="n">
-        <v>1682.9</v>
+        <v>746.88</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -4962,86 +4990,98 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S014→O01 下降</t>
+          <t>O01→S012 巡航</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1682.9</v>
+        <v>746.88</v>
       </c>
       <c r="D46" t="n">
-        <v>1868.6</v>
+        <v>978.47</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>O01→S010 爬升</t>
+          <t>O01→S012 下降</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>390</v>
+        <v>978.47</v>
       </c>
       <c r="D47" t="n">
-        <v>492.6</v>
+        <v>1031.87</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>O01→S010 巡航</t>
+          <t>S012 投送</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>492.6</v>
+        <v>1031.87</v>
       </c>
       <c r="D48" t="n">
-        <v>756.6</v>
+        <v>1271.87</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>O01→S010 巡航</t>
+          <t>S012→O01 爬升</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>756.6</v>
+        <v>1271.87</v>
       </c>
       <c r="D49" t="n">
-        <v>811.2</v>
+        <v>1316.37</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5057,19 +5097,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>O01→S010 下降</t>
+          <t>S012→O01 巡航</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>811.2</v>
+        <v>1316.37</v>
       </c>
       <c r="D50" t="n">
-        <v>844.8</v>
+        <v>1809.65</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5085,19 +5125,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S010 投送</t>
+          <t>S012→O01 下降</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>844.8</v>
+        <v>1809.65</v>
       </c>
       <c r="D51" t="n">
-        <v>1084.8</v>
+        <v>1899.09</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5113,30 +5153,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S010→O01 爬升</t>
+          <t>S012→O01 下降</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1084.8</v>
+        <v>1899.09</v>
       </c>
       <c r="D52" t="n">
-        <v>1112.8</v>
+        <v>1923.89</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5146,25 +5182,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S010→O01 巡航</t>
+          <t>O01→S011 爬升</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1112.8</v>
+        <v>360</v>
       </c>
       <c r="D53" t="n">
-        <v>1168.8</v>
+        <v>415.22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5174,14 +5206,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S010→O01 巡航</t>
+          <t>O01→S011 巡航</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1168.8</v>
+        <v>415.22</v>
       </c>
       <c r="D54" t="n">
-        <v>1431.4</v>
+        <v>603.03</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5198,14 +5230,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S010→O01 下降</t>
+          <t>O01→S011 下降</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1431.4</v>
+        <v>603.03</v>
       </c>
       <c r="D55" t="n">
-        <v>1554.6</v>
+        <v>635.53</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5217,19 +5249,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>O01→S006 爬升</t>
+          <t>S011 投送</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>510</v>
+        <v>635.53</v>
       </c>
       <c r="D56" t="n">
-        <v>605.4</v>
+        <v>845.53</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5241,19 +5273,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>O01→S006 巡航</t>
+          <t>S011→O01 爬升</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>605.4</v>
+        <v>845.53</v>
       </c>
       <c r="D57" t="n">
-        <v>817.4</v>
+        <v>872.61</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5265,19 +5297,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O01→S006 下降</t>
+          <t>S011→O01 巡航</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>817.4</v>
+        <v>872.61</v>
       </c>
       <c r="D58" t="n">
-        <v>843.1</v>
+        <v>1060.42</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -5289,19 +5321,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S006 投送</t>
+          <t>S011→O01 下降</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>843.1</v>
+        <v>1060.42</v>
       </c>
       <c r="D59" t="n">
-        <v>1167.1</v>
+        <v>1126.68</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5318,14 +5350,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S006→S001 爬升</t>
+          <t>O01→S001 爬升</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1167.1</v>
+        <v>510</v>
       </c>
       <c r="D60" t="n">
-        <v>1198.7</v>
+        <v>568.14</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -5342,14 +5374,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S006→S001 巡航</t>
+          <t>O01→S001 巡航</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1198.7</v>
+        <v>568.14</v>
       </c>
       <c r="D61" t="n">
-        <v>1551.8</v>
+        <v>772.37</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5366,14 +5398,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S006→S001 下降</t>
+          <t>O01→S001 下降</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1551.8</v>
+        <v>772.37</v>
       </c>
       <c r="D62" t="n">
-        <v>1656.8</v>
+        <v>816.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5394,10 +5426,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1656.8</v>
+        <v>816.9</v>
       </c>
       <c r="D63" t="n">
-        <v>1944.8</v>
+        <v>1248.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -5418,10 +5450,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1944.8</v>
+        <v>1248.9</v>
       </c>
       <c r="D64" t="n">
-        <v>1980.4</v>
+        <v>1284.52</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -5442,10 +5474,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1980.4</v>
+        <v>1284.52</v>
       </c>
       <c r="D65" t="n">
-        <v>2184.7</v>
+        <v>1488.75</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -5466,10 +5498,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2184.7</v>
+        <v>1488.75</v>
       </c>
       <c r="D66" t="n">
-        <v>2257.3</v>
+        <v>1561.43</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -5486,14 +5518,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>O01→S002 爬升</t>
+          <t>O01→S001 爬升</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="D67" t="n">
-        <v>552.5</v>
+        <v>598.14</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -5510,14 +5542,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S001 巡航</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>552.5</v>
+        <v>598.14</v>
       </c>
       <c r="D68" t="n">
-        <v>816.5</v>
+        <v>802.37</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -5534,25 +5566,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S001 下降</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>816.5</v>
+        <v>802.37</v>
       </c>
       <c r="D69" t="n">
-        <v>1048.2</v>
+        <v>846.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5562,25 +5590,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>O01→S002 下降</t>
+          <t>S001 投送</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1048.2</v>
+        <v>846.9</v>
       </c>
       <c r="D70" t="n">
-        <v>1092.9</v>
+        <v>1314.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5590,25 +5614,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S002 投送</t>
+          <t>S001→O01 爬升</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1092.9</v>
+        <v>1314.9</v>
       </c>
       <c r="D71" t="n">
-        <v>1488.9</v>
+        <v>1350.52</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5618,25 +5638,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S002→O01 爬升</t>
+          <t>S001→O01 巡航</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1488.9</v>
+        <v>1350.52</v>
       </c>
       <c r="D72" t="n">
-        <v>1524.7</v>
+        <v>1554.75</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5646,42 +5662,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S002→O01 巡航</t>
+          <t>S001→O01 下降</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1524.7</v>
+        <v>1554.75</v>
       </c>
       <c r="D73" t="n">
-        <v>1757.7</v>
+        <v>1627.43</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S002→O01 巡航</t>
+          <t>O01→S010 爬升</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1757.7</v>
+        <v>1516.7</v>
       </c>
       <c r="D74" t="n">
-        <v>2020.4</v>
+        <v>1619.35</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -5693,19 +5705,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>S002→O01 下降</t>
+          <t>O01→S010 巡航</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2020.4</v>
+        <v>1619.35</v>
       </c>
       <c r="D75" t="n">
-        <v>2111</v>
+        <v>1880.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -5722,21 +5734,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>O01→S010 巡航</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1672.5</v>
+        <v>1880.9</v>
       </c>
       <c r="D76" t="n">
-        <v>1720.9</v>
+        <v>1937.92</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5746,21 +5762,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>O01→S010 下降</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1720.9</v>
+        <v>1937.92</v>
       </c>
       <c r="D77" t="n">
-        <v>1976.2</v>
+        <v>1971.53</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5770,21 +5790,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S010 投送</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1976.2</v>
+        <v>1971.53</v>
       </c>
       <c r="D78" t="n">
-        <v>2011.8</v>
+        <v>2211.53</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5794,21 +5818,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S010→O01 爬升</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2011.8</v>
+        <v>2211.53</v>
       </c>
       <c r="D79" t="n">
-        <v>2221.8</v>
+        <v>2239.55</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5818,21 +5846,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S010→O01 巡航</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2221.8</v>
+        <v>2239.55</v>
       </c>
       <c r="D80" t="n">
-        <v>2251.5</v>
+        <v>2558.12</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5842,21 +5874,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S010→O01 下降</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2251.5</v>
+        <v>2558.12</v>
       </c>
       <c r="D81" t="n">
-        <v>2506.8</v>
+        <v>2656.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5866,14 +5902,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S010→O01 下降</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2506.8</v>
+        <v>2656.5</v>
       </c>
       <c r="D82" t="n">
-        <v>2565</v>
+        <v>2681.3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5890,14 +5926,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1672.6</v>
+        <v>1672.7</v>
       </c>
       <c r="D83" t="n">
-        <v>1721.1</v>
+        <v>1752.17</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -5914,14 +5950,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1721.1</v>
+        <v>1752.17</v>
       </c>
       <c r="D84" t="n">
-        <v>1976.4</v>
+        <v>2017.25</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5938,14 +5974,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1976.4</v>
+        <v>2017.25</v>
       </c>
       <c r="D85" t="n">
-        <v>2012</v>
+        <v>2037.77</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -5962,14 +5998,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2012</v>
+        <v>2037.77</v>
       </c>
       <c r="D86" t="n">
-        <v>2222</v>
+        <v>2247.77</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -5986,14 +6022,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S006→O01 爬升</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2222</v>
+        <v>2247.77</v>
       </c>
       <c r="D87" t="n">
-        <v>2251.7</v>
+        <v>2264.87</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -6010,14 +6046,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S006→O01 巡航</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2251.7</v>
+        <v>2264.87</v>
       </c>
       <c r="D88" t="n">
-        <v>2506.9</v>
+        <v>2529.95</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -6034,14 +6070,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S006→O01 下降</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2506.9</v>
+        <v>2529.95</v>
       </c>
       <c r="D89" t="n">
-        <v>2565.1</v>
+        <v>2625.31</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6058,14 +6094,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>O01→S012 爬升</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1944.6</v>
+        <v>2071.5</v>
       </c>
       <c r="D90" t="n">
-        <v>2039.8</v>
+        <v>2166.86</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -6082,14 +6118,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>O01→S012 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2039.8</v>
+        <v>2166.86</v>
       </c>
       <c r="D91" t="n">
-        <v>2303.8</v>
+        <v>2378.93</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -6106,25 +6142,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>O01→S012 巡航</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2303.8</v>
+        <v>2378.93</v>
       </c>
       <c r="D92" t="n">
-        <v>2533.1</v>
+        <v>2404.58</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6134,25 +6166,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>O01→S012 下降</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2533.1</v>
+        <v>2404.58</v>
       </c>
       <c r="D93" t="n">
-        <v>2586.5</v>
+        <v>2656.58</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6162,25 +6190,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S012 投送</t>
+          <t>S006→S007 爬升</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2586.5</v>
+        <v>2656.58</v>
       </c>
       <c r="D94" t="n">
-        <v>2826.5</v>
+        <v>2766.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6190,25 +6214,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S012→O01 爬升</t>
+          <t>S006→S007 巡航</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2826.5</v>
+        <v>2766.8</v>
       </c>
       <c r="D95" t="n">
-        <v>2871</v>
+        <v>2881.35</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6218,14 +6238,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S012→O01 巡航</t>
+          <t>S006→S007 巡航</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2871</v>
+        <v>2881.35</v>
       </c>
       <c r="D96" t="n">
-        <v>3102</v>
+        <v>2934.57</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6234,7 +6254,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -6246,21 +6266,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S012→O01 巡航</t>
+          <t>S006→S007 下降</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3102</v>
+        <v>2934.57</v>
       </c>
       <c r="D97" t="n">
-        <v>3364.2</v>
+        <v>3055.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6270,110 +6294,126 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S012→O01 下降</t>
+          <t>S007 投送</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3364.2</v>
+        <v>3055.5</v>
       </c>
       <c r="D98" t="n">
-        <v>3478.5</v>
+        <v>3415.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S007→O01 爬升</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2228.6</v>
+        <v>3415.5</v>
       </c>
       <c r="D99" t="n">
-        <v>2277</v>
+        <v>3480.89</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S007→O01 巡航</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2277</v>
+        <v>3480.89</v>
       </c>
       <c r="D100" t="n">
-        <v>2481.3</v>
+        <v>3783.16</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S007→O01 下降</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2481.3</v>
+        <v>3783.16</v>
       </c>
       <c r="D101" t="n">
-        <v>2516.9</v>
+        <v>3968.99</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S007→O01 下降</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2516.9</v>
+        <v>3968.99</v>
       </c>
       <c r="D102" t="n">
-        <v>2726.9</v>
+        <v>3975.3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6390,14 +6430,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>O01→S011 爬升</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2726.9</v>
+        <v>2002.1</v>
       </c>
       <c r="D103" t="n">
-        <v>2756.6</v>
+        <v>2057.32</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6414,14 +6454,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>O01→S011 巡航</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2756.6</v>
+        <v>2057.32</v>
       </c>
       <c r="D104" t="n">
-        <v>2960.8</v>
+        <v>2292.08</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6438,14 +6478,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>O01→S011 下降</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2960.8</v>
+        <v>2292.08</v>
       </c>
       <c r="D105" t="n">
-        <v>3019</v>
+        <v>2324.58</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -6457,19 +6497,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>O01→S007 爬升</t>
+          <t>S011 投送</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2621</v>
+        <v>2324.58</v>
       </c>
       <c r="D106" t="n">
-        <v>2774.7</v>
+        <v>2504.58</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -6481,19 +6521,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>S011→S015 爬升</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2774.7</v>
+        <v>2504.58</v>
       </c>
       <c r="D107" t="n">
-        <v>3037.7</v>
+        <v>2629.96</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -6505,47 +6545,43 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>S011→S015 巡航</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3037.7</v>
+        <v>2629.96</v>
       </c>
       <c r="D108" t="n">
-        <v>3077</v>
+        <v>2747.69</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>O01→S007 下降</t>
+          <t>S011→S015 巡航</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3077</v>
+        <v>2747.69</v>
       </c>
       <c r="D109" t="n">
-        <v>3158.8</v>
+        <v>2918.48</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -6561,19 +6597,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>S007 投送</t>
+          <t>S011→S015 下降</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3158.8</v>
+        <v>2918.48</v>
       </c>
       <c r="D110" t="n">
-        <v>3446.8</v>
+        <v>2963.97</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -6589,19 +6625,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S007→S003 爬升</t>
+          <t>S015 投送</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3446.8</v>
+        <v>2963.97</v>
       </c>
       <c r="D111" t="n">
-        <v>3471.6</v>
+        <v>3143.97</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -6617,19 +6653,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S007→S003 巡航</t>
+          <t>S015→S003 爬升</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3471.6</v>
+        <v>3143.97</v>
       </c>
       <c r="D112" t="n">
-        <v>3653.9</v>
+        <v>3148.44</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6645,19 +6681,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>S007→S003 下降</t>
+          <t>S015→S003 巡航</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3653.9</v>
+        <v>3148.44</v>
       </c>
       <c r="D113" t="n">
-        <v>3690</v>
+        <v>3366.35</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -6673,19 +6709,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S003 投送</t>
+          <t>S015→S003 下降</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3690</v>
+        <v>3366.35</v>
       </c>
       <c r="D114" t="n">
-        <v>4014</v>
+        <v>3426.11</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6701,19 +6737,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S003→O01 爬升</t>
+          <t>S003 投送</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4014</v>
+        <v>3426.11</v>
       </c>
       <c r="D115" t="n">
-        <v>4103.3</v>
+        <v>3606.11</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6729,19 +6765,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S003→O01 爬升</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4103.3</v>
+        <v>3606.11</v>
       </c>
       <c r="D116" t="n">
-        <v>4325.3</v>
+        <v>3680.55</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -6757,7 +6793,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6766,22 +6802,26 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4325.3</v>
+        <v>3680.55</v>
       </c>
       <c r="D117" t="n">
-        <v>4587.4</v>
+        <v>4285.69</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6790,34 +6830,38 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4587.4</v>
+        <v>4285.69</v>
       </c>
       <c r="D118" t="n">
-        <v>4804.4</v>
+        <v>4453.99</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>O01→S011 爬升</t>
+          <t>S003→O01 下降</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2538.8</v>
+        <v>4453.99</v>
       </c>
       <c r="D119" t="n">
-        <v>2594</v>
+        <v>4459.33</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6829,19 +6873,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>O01→S011 巡航</t>
+          <t>O01→S002 爬升</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2594</v>
+        <v>2137.5</v>
       </c>
       <c r="D120" t="n">
-        <v>2828.8</v>
+        <v>2210</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -6853,19 +6897,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>O01→S011 下降</t>
+          <t>O01→S002 巡航</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2828.8</v>
+        <v>2210</v>
       </c>
       <c r="D121" t="n">
-        <v>2861.3</v>
+        <v>2472.07</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6877,139 +6921,159 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>S011 投送</t>
+          <t>O01→S002 巡航</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2861.3</v>
+        <v>2472.07</v>
       </c>
       <c r="D122" t="n">
-        <v>3071.3</v>
+        <v>2705.7</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>S011→O01 爬升</t>
+          <t>O01→S002 下降</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3071.3</v>
+        <v>2705.7</v>
       </c>
       <c r="D123" t="n">
-        <v>3098.4</v>
+        <v>2750.43</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S011→O01 巡航</t>
+          <t>S002 投送</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3098.4</v>
+        <v>2750.43</v>
       </c>
       <c r="D124" t="n">
-        <v>3333.1</v>
+        <v>3182.43</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>S011→O01 下降</t>
+          <t>S002→O01 爬升</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3333.1</v>
+        <v>3182.43</v>
       </c>
       <c r="D125" t="n">
-        <v>3399.4</v>
+        <v>3218.21</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S002→O01 巡航</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2767.3</v>
+        <v>3218.21</v>
       </c>
       <c r="D126" t="n">
-        <v>2825.5</v>
+        <v>3451.24</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S002→O01 巡航</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2825.5</v>
+        <v>3451.24</v>
       </c>
       <c r="D127" t="n">
-        <v>3029.7</v>
+        <v>3713.91</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -7021,19 +7085,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S002→O01 下降</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3029.7</v>
+        <v>3713.91</v>
       </c>
       <c r="D128" t="n">
-        <v>3074.2</v>
+        <v>3804.54</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -7045,19 +7109,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>O01→S014 爬升</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3074.2</v>
+        <v>2313.9</v>
       </c>
       <c r="D129" t="n">
-        <v>3362.2</v>
+        <v>2468.65</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -7069,19 +7133,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S001→S005 爬升</t>
+          <t>O01→S014 巡航</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3362.2</v>
+        <v>2468.65</v>
       </c>
       <c r="D130" t="n">
-        <v>3415.1</v>
+        <v>2729.27</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -7093,43 +7157,47 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>S001→S005 巡航</t>
+          <t>O01→S014 巡航</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3415.1</v>
+        <v>2729.27</v>
       </c>
       <c r="D131" t="n">
-        <v>3503.1</v>
+        <v>2829.37</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>S001→S005 巡航</t>
+          <t>O01→S014 下降</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3503.1</v>
+        <v>2829.37</v>
       </c>
       <c r="D132" t="n">
-        <v>3610.8</v>
+        <v>2925.75</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -7138,26 +7206,26 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>S001→S005 下降</t>
+          <t>S014 投送</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3610.8</v>
+        <v>2925.75</v>
       </c>
       <c r="D133" t="n">
-        <v>3671.4</v>
+        <v>3165.75</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -7166,26 +7234,26 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>S005 投送</t>
+          <t>S014→O01 爬升</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3671.4</v>
+        <v>3165.75</v>
       </c>
       <c r="D134" t="n">
-        <v>3995.4</v>
+        <v>3246.07</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -7194,26 +7262,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>S005→O01 爬升</t>
+          <t>S014→O01 巡航</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3995.4</v>
+        <v>3246.07</v>
       </c>
       <c r="D135" t="n">
-        <v>4047.9</v>
+        <v>3450.6</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -7222,54 +7290,50 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S014→O01 巡航</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4047.9</v>
+        <v>3450.6</v>
       </c>
       <c r="D136" t="n">
-        <v>4137.9</v>
+        <v>3606.79</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S014→O01 下降</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4137.9</v>
+        <v>3606.79</v>
       </c>
       <c r="D137" t="n">
-        <v>4401.4</v>
+        <v>3792.49</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -7286,14 +7350,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>S005→O01 下降</t>
+          <t>O01→S015 爬升</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4401.4</v>
+        <v>2551</v>
       </c>
       <c r="D138" t="n">
-        <v>4500.8</v>
+        <v>2699.03</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -7305,19 +7369,19 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>O01→S011 爬升</t>
+          <t>O01→S015 巡航</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2856.8</v>
+        <v>2699.03</v>
       </c>
       <c r="D139" t="n">
-        <v>2912</v>
+        <v>3025.36</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -7329,139 +7393,159 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>O01→S011 巡航</t>
+          <t>O01→S015 巡航</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2912</v>
+        <v>3025.36</v>
       </c>
       <c r="D140" t="n">
-        <v>3146.8</v>
+        <v>3200.66</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>O01→S011 下降</t>
+          <t>O01→S015 下降</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3146.8</v>
+        <v>3200.66</v>
       </c>
       <c r="D141" t="n">
-        <v>3179.3</v>
+        <v>3239.58</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S011 投送</t>
+          <t>S015 投送</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3179.3</v>
+        <v>3239.58</v>
       </c>
       <c r="D142" t="n">
-        <v>3359.3</v>
+        <v>3449.58</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S011→S005 爬升</t>
+          <t>S015→O01 爬升</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3359.3</v>
+        <v>3449.58</v>
       </c>
       <c r="D143" t="n">
-        <v>3404.4</v>
+        <v>3482.01</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 巡航</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3404.4</v>
+        <v>3482.01</v>
       </c>
       <c r="D144" t="n">
-        <v>3517.4</v>
+        <v>3983.64</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 下降</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3517.4</v>
+        <v>3983.64</v>
       </c>
       <c r="D145" t="n">
-        <v>3554.4</v>
+        <v>4155.96</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -7477,19 +7561,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 下降</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3554.4</v>
+        <v>4155.96</v>
       </c>
       <c r="D146" t="n">
-        <v>3559.4</v>
+        <v>4161.28</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -7506,25 +7590,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 爬升</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3559.4</v>
+        <v>3041.3</v>
       </c>
       <c r="D147" t="n">
-        <v>3585.4</v>
+        <v>3123.04</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7534,14 +7614,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 巡航</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3585.4</v>
+        <v>3123.04</v>
       </c>
       <c r="D148" t="n">
-        <v>3633.4</v>
+        <v>3415.57</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -7558,14 +7638,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 巡航</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3633.4</v>
+        <v>3415.57</v>
       </c>
       <c r="D149" t="n">
-        <v>3638.8</v>
+        <v>3663.67</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7586,14 +7666,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>S011→S005 下降</t>
+          <t>O01→S008 下降</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3638.8</v>
+        <v>3663.67</v>
       </c>
       <c r="D150" t="n">
-        <v>3699.9</v>
+        <v>3704.48</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7614,14 +7694,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>S005 投送</t>
+          <t>S008 投送</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3699.9</v>
+        <v>3704.48</v>
       </c>
       <c r="D151" t="n">
-        <v>3909.9</v>
+        <v>3914.48</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7642,14 +7722,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>S005→O01 爬升</t>
+          <t>S008→O01 爬升</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3909.9</v>
+        <v>3914.48</v>
       </c>
       <c r="D152" t="n">
-        <v>3953.7</v>
+        <v>3948.48</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7670,14 +7750,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S008→O01 巡航</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3953.7</v>
+        <v>3948.48</v>
       </c>
       <c r="D153" t="n">
-        <v>4066.7</v>
+        <v>4489.12</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -7698,21 +7778,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4066.7</v>
+        <v>4489.12</v>
       </c>
       <c r="D154" t="n">
-        <v>4395.5</v>
+        <v>4581.87</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7722,14 +7806,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>S005→O01 下降</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4395.5</v>
+        <v>4581.87</v>
       </c>
       <c r="D155" t="n">
-        <v>4475</v>
+        <v>4587.2</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7746,14 +7830,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>O01→S008 爬升</t>
+          <t>O01→S005 爬升</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3379</v>
+        <v>3057.2</v>
       </c>
       <c r="D156" t="n">
-        <v>3460.7</v>
+        <v>3123.44</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7770,14 +7854,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>O01→S008 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3460.7</v>
+        <v>3123.44</v>
       </c>
       <c r="D157" t="n">
-        <v>3754.7</v>
+        <v>3451.3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7794,14 +7878,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>O01→S008 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3754.7</v>
+        <v>3451.3</v>
       </c>
       <c r="D158" t="n">
-        <v>4001.3</v>
+        <v>3565.27</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -7822,14 +7906,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>O01→S008 下降</t>
+          <t>O01→S005 下降</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4001.3</v>
+        <v>3565.27</v>
       </c>
       <c r="D159" t="n">
-        <v>4042.1</v>
+        <v>3617.84</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -7850,14 +7934,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>S008 投送</t>
+          <t>S005 投送</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4042.1</v>
+        <v>3617.84</v>
       </c>
       <c r="D160" t="n">
-        <v>4252.1</v>
+        <v>3827.84</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -7878,14 +7962,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>S008→O01 爬升</t>
+          <t>S005→O01 爬升</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4252.1</v>
+        <v>3827.84</v>
       </c>
       <c r="D161" t="n">
-        <v>4286.1</v>
+        <v>3871.64</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -7906,14 +7990,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S005→O01 巡航</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4286.1</v>
+        <v>3871.64</v>
       </c>
       <c r="D162" t="n">
-        <v>4533.1</v>
+        <v>4313.47</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -7934,21 +8018,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S005→O01 下降</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4533.1</v>
+        <v>4313.47</v>
       </c>
       <c r="D163" t="n">
-        <v>4826.8</v>
+        <v>4387.65</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7958,14 +8046,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>S008→O01 下降</t>
+          <t>S005→O01 下降</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4826.8</v>
+        <v>4387.65</v>
       </c>
       <c r="D164" t="n">
-        <v>4924.9</v>
+        <v>4392.96</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -7986,10 +8074,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3868.5</v>
+        <v>4182.5</v>
       </c>
       <c r="D165" t="n">
-        <v>3950.2</v>
+        <v>4264.24</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -8010,10 +8098,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3950.2</v>
+        <v>4264.24</v>
       </c>
       <c r="D166" t="n">
-        <v>4244.2</v>
+        <v>4556.77</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -8034,10 +8122,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4244.2</v>
+        <v>4556.77</v>
       </c>
       <c r="D167" t="n">
-        <v>4490.9</v>
+        <v>4804.87</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -8062,10 +8150,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4490.9</v>
+        <v>4804.87</v>
       </c>
       <c r="D168" t="n">
-        <v>4531.7</v>
+        <v>4845.68</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -8090,10 +8178,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4531.7</v>
+        <v>4845.68</v>
       </c>
       <c r="D169" t="n">
-        <v>4771.7</v>
+        <v>5085.68</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -8118,10 +8206,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4771.7</v>
+        <v>5085.68</v>
       </c>
       <c r="D170" t="n">
-        <v>4805.7</v>
+        <v>5119.68</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -8146,10 +8234,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4805.7</v>
+        <v>5119.68</v>
       </c>
       <c r="D171" t="n">
-        <v>5052.7</v>
+        <v>5660.32</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -8170,21 +8258,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5052.7</v>
+        <v>5660.32</v>
       </c>
       <c r="D172" t="n">
-        <v>5346.3</v>
+        <v>5753.07</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8198,10 +8290,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5346.3</v>
+        <v>5753.07</v>
       </c>
       <c r="D173" t="n">
-        <v>5444.4</v>
+        <v>5758.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -8218,14 +8310,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>O01→S007 爬升</t>
+          <t>O01→S005 爬升</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4980.8</v>
+        <v>4344.6</v>
       </c>
       <c r="D174" t="n">
-        <v>5134.5</v>
+        <v>4424.08</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -8242,14 +8334,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5134.5</v>
+        <v>4424.08</v>
       </c>
       <c r="D175" t="n">
-        <v>5397.5</v>
+        <v>4686.08</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -8266,14 +8358,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5397.5</v>
+        <v>4686.08</v>
       </c>
       <c r="D176" t="n">
-        <v>5436.7</v>
+        <v>4777.55</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -8294,14 +8386,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>O01→S007 下降</t>
+          <t>O01→S005 下降</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5436.7</v>
+        <v>4777.55</v>
       </c>
       <c r="D177" t="n">
-        <v>5518.5</v>
+        <v>4843.26</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8322,14 +8414,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>S007 投送</t>
+          <t>S005 投送</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5518.5</v>
+        <v>4843.26</v>
       </c>
       <c r="D178" t="n">
-        <v>5770.5</v>
+        <v>5167.26</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8350,14 +8442,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>S007→S003 爬升</t>
+          <t>S005→S004 爬升</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5770.5</v>
+        <v>5167.26</v>
       </c>
       <c r="D179" t="n">
-        <v>5795.4</v>
+        <v>5235.58</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8378,14 +8470,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S007→S003 巡航</t>
+          <t>S005→S004 巡航</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5795.4</v>
+        <v>5235.58</v>
       </c>
       <c r="D180" t="n">
-        <v>5977.6</v>
+        <v>5410.03</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8406,14 +8498,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S007→S003 下降</t>
+          <t>S005→S004 下降</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5977.6</v>
+        <v>5410.03</v>
       </c>
       <c r="D181" t="n">
-        <v>6013.7</v>
+        <v>5460.17</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8434,14 +8526,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S003 投送</t>
+          <t>S005→S004 下降</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6013.7</v>
+        <v>5460.17</v>
       </c>
       <c r="D182" t="n">
-        <v>6337.7</v>
+        <v>5478.78</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -8450,7 +8542,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -8462,14 +8554,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S003→O01 爬升</t>
+          <t>S004 投送</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6337.7</v>
+        <v>5478.78</v>
       </c>
       <c r="D183" t="n">
-        <v>6427</v>
+        <v>5802.78</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -8478,7 +8570,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -8490,14 +8582,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S004→O01 爬升</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6427</v>
+        <v>5802.78</v>
       </c>
       <c r="D184" t="n">
-        <v>6649</v>
+        <v>5870.75</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -8506,7 +8598,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -8518,21 +8610,25 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6649</v>
+        <v>5870.75</v>
       </c>
       <c r="D185" t="n">
-        <v>6911.1</v>
+        <v>6031.27</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8542,14 +8638,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S003→O01 下降</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>6911.1</v>
+        <v>6031.27</v>
       </c>
       <c r="D186" t="n">
-        <v>7128.2</v>
+        <v>6387.13</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -8561,19 +8657,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>O01→S004 爬升</t>
+          <t>S004→O01 下降</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>5284.4</v>
+        <v>6387.13</v>
       </c>
       <c r="D187" t="n">
-        <v>5392.7</v>
+        <v>6522.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -8590,14 +8686,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>O01→S004 巡航</t>
+          <t>O01→S003 爬升</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5392.7</v>
+        <v>4485.3</v>
       </c>
       <c r="D188" t="n">
-        <v>5767.7</v>
+        <v>4658.94</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -8614,25 +8710,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>O01→S004 巡航</t>
+          <t>O01→S003 巡航</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5767.7</v>
+        <v>4658.94</v>
       </c>
       <c r="D189" t="n">
-        <v>5909</v>
+        <v>4919.77</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8642,14 +8734,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>O01→S004 下降</t>
+          <t>O01→S003 巡航</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>5909</v>
+        <v>4919.77</v>
       </c>
       <c r="D190" t="n">
-        <v>5977</v>
+        <v>5143.06</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -8670,14 +8762,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>O01→S004 下降</t>
+          <t>O01→S003 下降</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5977</v>
+        <v>5143.06</v>
       </c>
       <c r="D191" t="n">
-        <v>5994</v>
+        <v>5254.71</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -8686,7 +8778,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -8698,14 +8790,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S004 投送</t>
+          <t>S003 投送</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>5994</v>
+        <v>5254.71</v>
       </c>
       <c r="D192" t="n">
-        <v>6390</v>
+        <v>5686.71</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -8714,7 +8806,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -8726,14 +8818,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>S004→O01 爬升</t>
+          <t>S003→O01 爬升</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>6390</v>
+        <v>5686.71</v>
       </c>
       <c r="D193" t="n">
-        <v>6458</v>
+        <v>5776.03</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -8742,7 +8834,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -8754,14 +8846,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>S004→O01 巡航</t>
+          <t>S003→O01 巡航</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6458</v>
+        <v>5776.03</v>
       </c>
       <c r="D194" t="n">
-        <v>6600</v>
+        <v>5998.52</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -8770,7 +8862,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -8782,14 +8874,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S004→O01 巡航</t>
+          <t>S003→O01 巡航</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>6600</v>
+        <v>5998.52</v>
       </c>
       <c r="D195" t="n">
-        <v>6974.4</v>
+        <v>6260.14</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -8806,14 +8898,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>S004→O01 下降</t>
+          <t>S003→O01 下降</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>6974.4</v>
+        <v>6260.14</v>
       </c>
       <c r="D196" t="n">
-        <v>7109.6</v>
+        <v>6477.2</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -8830,14 +8922,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>O01→S015 爬升</t>
+          <t>O01→S004 爬升</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5314.9</v>
+        <v>4947.3</v>
       </c>
       <c r="D197" t="n">
-        <v>5462.9</v>
+        <v>5037.48</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -8854,14 +8946,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>O01→S015 巡航</t>
+          <t>O01→S004 巡航</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5462.9</v>
+        <v>5037.48</v>
       </c>
       <c r="D198" t="n">
-        <v>5725.9</v>
+        <v>5410.99</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -8878,14 +8970,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>O01→S015 巡航</t>
+          <t>O01→S004 巡航</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5725.9</v>
+        <v>5410.99</v>
       </c>
       <c r="D199" t="n">
-        <v>5864.2</v>
+        <v>5553.86</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -8906,14 +8998,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>O01→S015 下降</t>
+          <t>O01→S004 下降</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5864.2</v>
+        <v>5553.86</v>
       </c>
       <c r="D200" t="n">
-        <v>5903.1</v>
+        <v>5606.66</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -8934,14 +9026,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>S015 投送</t>
+          <t>O01→S004 下降</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5903.1</v>
+        <v>5606.66</v>
       </c>
       <c r="D201" t="n">
-        <v>6143.1</v>
+        <v>5621.83</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -8950,7 +9042,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -8962,14 +9054,14 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>S015→O01 爬升</t>
+          <t>S004 投送</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>6143.1</v>
+        <v>5621.83</v>
       </c>
       <c r="D202" t="n">
-        <v>6175.5</v>
+        <v>5831.83</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -8978,7 +9070,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -8990,14 +9082,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>S015→O01 巡航</t>
+          <t>S004→O01 爬升</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>6175.5</v>
+        <v>5831.83</v>
       </c>
       <c r="D203" t="n">
-        <v>6315.5</v>
+        <v>5888.48</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9006,7 +9098,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -9018,21 +9110,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>S015→O01 巡航</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6315.5</v>
+        <v>5888.48</v>
       </c>
       <c r="D204" t="n">
-        <v>6576.8</v>
+        <v>6031.3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9042,14 +9138,14 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>S015→O01 下降</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>6576.8</v>
+        <v>6031.3</v>
       </c>
       <c r="D205" t="n">
-        <v>6754.5</v>
+        <v>6404.86</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9061,19 +9157,19 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>O01→S009 爬升</t>
+          <t>S004→O01 下降</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>5834.4</v>
+        <v>6404.86</v>
       </c>
       <c r="D206" t="n">
-        <v>5889.6</v>
+        <v>6513.07</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -9081,218 +9177,6 @@
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>O01→S009 巡航</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>5889.6</v>
-      </c>
-      <c r="D207" t="n">
-        <v>6153.6</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>O01→S009 巡航</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>6153.6</v>
-      </c>
-      <c r="D208" t="n">
-        <v>6271.1</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>O01→S009 下降</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>6271.1</v>
-      </c>
-      <c r="D209" t="n">
-        <v>6296.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>S009 投送</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>6296.4</v>
-      </c>
-      <c r="D210" t="n">
-        <v>6536.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>S009→O01 爬升</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>6536.4</v>
-      </c>
-      <c r="D211" t="n">
-        <v>6557.5</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>S009→O01 巡航</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>6557.5</v>
-      </c>
-      <c r="D212" t="n">
-        <v>6675.5</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>S009→O01 巡航</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>6675.5</v>
-      </c>
-      <c r="D213" t="n">
-        <v>6939</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>S009→O01 下降</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>6939</v>
-      </c>
-      <c r="D214" t="n">
-        <v>7005.2</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9376,11 +9260,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015</t>
+          <t>S001,S004,S005,S006,S007,S010</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -9389,7 +9273,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -9398,10 +9282,10 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -9415,11 +9299,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S002,S004,S008,S009,S010,S012,S013,S014</t>
+          <t>S002,S003,S008,S009,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -9428,13 +9312,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -9454,11 +9338,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S003,S005,S006,S007,S011,S015</t>
+          <t>S001,S003,S006,S007,S011,S015</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -9467,7 +9351,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -9493,32 +9377,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002,S004,S013</t>
+          <t>S002,S004,S005,S009,S010,S013</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -9532,7 +9416,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S008,S009,S010,S012,S014</t>
+          <t>S008,S012,S014</t>
         </is>
       </c>
       <c r="D6" t="n">
